--- a/data/trans_dic/IP7_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP7_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general regular o mala</t>
+          <t>Menores con salud general regular o mala (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 9,97</t>
+          <t>2,12; 9,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,43</t>
+          <t>0,71; 6,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 9,95</t>
+          <t>0,9; 10,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 42,23</t>
+          <t>1,25; 42,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 10,3</t>
+          <t>2,38; 11,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 9,33</t>
+          <t>1,7; 9,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,92</t>
+          <t>0,12; 7,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 15,62</t>
+          <t>3,04; 16,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 8,66</t>
+          <t>3,09; 8,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,03</t>
+          <t>1,69; 6,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 7,01</t>
+          <t>1,14; 6,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 23,89</t>
+          <t>4,1; 24,52</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,84</t>
+          <t>0,8; 2,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,23</t>
+          <t>1,62; 4,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,45</t>
+          <t>1,26; 3,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,01</t>
+          <t>1,51; 4,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,89</t>
+          <t>2,19; 4,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,02</t>
+          <t>1,68; 3,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,75</t>
+          <t>1,37; 3,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,99</t>
+          <t>0,86; 2,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,48</t>
+          <t>1,79; 3,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,58</t>
+          <t>1,96; 3,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,13</t>
+          <t>1,52; 3,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,08</t>
+          <t>1,38; 2,95</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,98</t>
+          <t>0,53; 4,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,85</t>
+          <t>1,24; 5,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,14</t>
+          <t>0,37; 3,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,18</t>
+          <t>0,32; 3,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,75</t>
+          <t>1,28; 6,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,99</t>
+          <t>0,75; 2,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,73</t>
+          <t>0,39; 2,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,95</t>
+          <t>0,33; 1,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,52</t>
+          <t>1,21; 4,51</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,74</t>
+          <t>1,04; 2,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,49</t>
+          <t>1,42; 3,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,97</t>
+          <t>1,21; 2,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 6,2</t>
+          <t>1,85; 6,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,68</t>
+          <t>2,62; 4,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,48</t>
+          <t>1,64; 3,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,12</t>
+          <t>1,38; 3,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,6</t>
+          <t>1,61; 3,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,34</t>
+          <t>1,98; 3,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,2</t>
+          <t>1,83; 3,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,62</t>
+          <t>1,44; 2,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,38</t>
+          <t>2,04; 4,49</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con salud general regular o mala (tasa de respuesta: 99,72%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4503</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2397</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2205</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6953</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4811</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3710</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4725</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9313</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6107</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4225</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>11678</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1924; 8937</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>656; 5729</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>535; 6102</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>682; 23503</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2048; 9613</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1448; 8203</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>86; 5389</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1885; 10064</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5472; 14574</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2999; 11296</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1464; 8123</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4780; 28607</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12664</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10121</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11631</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16010</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12777</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11375</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8417</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>22519</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>25441</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>21496</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>20048</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3336; 11524</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7323; 20064</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5898; 16283</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6962; 20093</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10436; 23610</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8272; 19497</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>6663; 18133</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4452; 14095</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>15983; 30805</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>18489; 34618</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>14501; 30062</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>13472; 28873</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1558</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4594</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2240</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5527</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5226</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3798</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3176</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>8087</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3529</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5276</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3681</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>791; 7076</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1958; 9040</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>641; 6126</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>591; 5634</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2341; 11728</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2481; 9887</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1312; 8552</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1165; 6986</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4012; 15017</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>11645</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16619</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13398</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21144</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>25414</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>18726</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15499</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>18669</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>37059</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>35346</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>28897</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>39813</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7110; 18445</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10097; 23497</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>8476; 20490</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>12321; 41907</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>18836; 34253</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>12311; 26501</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>10206; 22578</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>12240; 28009</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>27780; 47500</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>26646; 46610</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>20816; 38452</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>29099; 64003</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>